--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486854_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486854_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0066</v>
+        <v>5.4062</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5164</v>
+        <v>2.9159</v>
       </c>
       <c r="F2" t="n">
         <v>2.4902</v>
@@ -610,10 +610,10 @@
         <v>2.6694</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0766</v>
+        <v>1.4761</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3016</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="U2" t="n">
         <v>0.775</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0235</v>
+        <v>3.1099</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4169</v>
+        <v>3.4441</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3934</v>
+        <v>-0.3342</v>
       </c>
       <c r="G3" t="n">
         <v>1.1653</v>
@@ -688,13 +688,13 @@
         <v>1.8481</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3921</v>
+        <v>0.4785</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0931</v>
+        <v>-0.066</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4852</v>
+        <v>0.5445</v>
       </c>
       <c r="V3" t="n">
         <v>1.8768</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4719</v>
+        <v>2.9924</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7219</v>
+        <v>3.2721</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.25</v>
+        <v>-0.2796</v>
       </c>
       <c r="G4" t="n">
         <v>0.1938</v>
@@ -766,13 +766,13 @@
         <v>2.8748</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9806</v>
+        <v>-0.4601</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3174</v>
+        <v>-0.7673</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3368</v>
+        <v>0.3072</v>
       </c>
       <c r="V4" t="n">
         <v>0.5893</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2359</v>
+        <v>1.3544</v>
       </c>
       <c r="E5" t="n">
         <v>1.3199</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0.0346</v>
       </c>
       <c r="G5" t="n">
         <v>-0.1763</v>
@@ -844,13 +844,13 @@
         <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.169</v>
+        <v>-0.0504</v>
       </c>
       <c r="T5" t="n">
         <v>0.1704</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3394</v>
+        <v>-0.2208</v>
       </c>
       <c r="V5" t="n">
         <v>0.3491</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5366</v>
+        <v>-0.6956</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1275</v>
+        <v>1.8796</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.6641</v>
+        <v>-2.5752</v>
       </c>
       <c r="G6" t="n">
         <v>1.064</v>
@@ -922,13 +922,13 @@
         <v>1.8481</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.2237</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0386</v>
+        <v>-0.2093</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1034</v>
+        <v>-0.0144</v>
       </c>
       <c r="V6" t="n">
         <v>-2.3573</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8293</v>
+        <v>-1.3904</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4653</v>
+        <v>-0.0856</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.364</v>
+        <v>-1.3047</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1917</v>
@@ -1000,13 +1000,13 @@
         <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.1453</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3952</v>
+        <v>-0.0156</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.189</v>
+        <v>-0.1297</v>
       </c>
       <c r="V7" t="n">
         <v>1.1786</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3049</v>
+        <v>-2.0504</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6221</v>
+        <v>-1.3082</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6828</v>
+        <v>-0.7421</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9163</v>
@@ -1078,13 +1078,13 @@
         <v>0.8214</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2449</v>
+        <v>0.0097</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3952</v>
+        <v>-0.0814</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1504</v>
+        <v>0.0911</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9384</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.9268</v>
+        <v>-3.5018</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5431</v>
+        <v>-3.0588</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3837</v>
+        <v>-0.443</v>
       </c>
       <c r="G9" t="n">
         <v>-2.8408</v>
@@ -1156,13 +1156,13 @@
         <v>1.6427</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3262</v>
+        <v>0.0988</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9222</v>
+        <v>-0.4379</v>
       </c>
       <c r="U9" t="n">
-        <v>0.596</v>
+        <v>0.5367</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3491</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. GARCIA ROSELLO</t>
+          <t>A. DUVAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4451</v>
+        <v>-4.3038</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1272</v>
+        <v>-3.6751</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3179</v>
+        <v>-0.6287</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7664</v>
+        <v>-4.5965</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4832</v>
+        <v>-1.6125</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.2496</v>
+        <v>-2.9841</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0198</v>
+        <v>-2.0951</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9538</v>
+        <v>-0.5027</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9737</v>
+        <v>-1.5924</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7465</v>
+        <v>-2.5014</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4706</v>
+        <v>-1.1098</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2759</v>
+        <v>-1.3917</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0801</v>
+        <v>-3.2855</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0267</v>
+        <v>2.2588</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6149</v>
+        <v>0.2721</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0272</v>
+        <v>0.2866</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6421</v>
+        <v>-0.0144</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2402</v>
+        <v>1.0472</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2402</v>
+        <v>-0.3716</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. CADME ARIAS</t>
+          <t>M. GARCIA ROSELLO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8671</v>
+        <v>-5.0784</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3219</v>
+        <v>-4.3751</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5452</v>
+        <v>-0.7033</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.2191</v>
+        <v>-2.7664</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.7378</v>
+        <v>0.4832</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4813</v>
+        <v>-3.2496</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4465</v>
+        <v>-1.0198</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.6833</v>
+        <v>0.9538</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2368</v>
+        <v>-1.9737</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7726</v>
+        <v>-1.7465</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0546</v>
+        <v>-0.4706</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7181</v>
+        <v>-1.2759</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2053</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2588</v>
+        <v>-3.0801</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4641</v>
+        <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2637</v>
+        <v>-0.0184</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1431</v>
+        <v>-0.2752</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1206</v>
+        <v>0.2568</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.117</v>
+        <v>-0.2402</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.3573</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. DUVAL</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0755</v>
+        <v>-5.0868</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1207</v>
+        <v>-2.123</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9548</v>
+        <v>-2.9638</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.5965</v>
+        <v>-2.9599</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6125</v>
+        <v>-0.7947</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.9841</v>
+        <v>-2.1653</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.0951</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5027</v>
+        <v>-0.7134</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.5924</v>
+        <v>0.0395</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5014</v>
+        <v>-2.286</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1098</v>
+        <v>-0.0813</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3917</v>
+        <v>-2.2047</v>
       </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-1.0267</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-3.2855</v>
-      </c>
       <c r="R12" t="n">
-        <v>2.2588</v>
+        <v>1.0267</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4995</v>
+        <v>-0.708</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.159</v>
+        <v>-0.4224</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3405</v>
+        <v>-0.2857</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0472</v>
+        <v>-1.4189</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3716</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>G. CADME ARIAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.1091</v>
+        <v>-5.1241</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2935</v>
+        <v>-3.6085</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8156</v>
+        <v>-1.5155</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.9599</v>
+        <v>-3.2191</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7947</v>
+        <v>-2.7378</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1653</v>
+        <v>-0.4813</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-1.4465</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7134</v>
+        <v>-1.6833</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0395</v>
+        <v>0.2368</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.286</v>
+        <v>-1.7726</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0813</v>
+        <v>-1.0546</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.2047</v>
+        <v>-0.7181</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.2053</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0267</v>
+        <v>-2.2588</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0267</v>
+        <v>2.4641</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7302999999999999</v>
+        <v>0.0067</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5928</v>
+        <v>-0.1435</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1374</v>
+        <v>0.1502</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4189</v>
+        <v>-2.117</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4189</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="14">
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.3565</v>
+        <v>-14.3684</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.3912</v>
+        <v>-5.402699999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.965299999999999</v>
+        <v>-8.965300000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-14.472</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.118800000000001</v>
+        <v>-1.1188</v>
       </c>
       <c r="I14" t="n">
         <v>-13.3533</v>
@@ -1522,10 +1522,10 @@
         <v>7.201000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>7.334799999999998</v>
+        <v>7.334799999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1341</v>
+        <v>-0.1341000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-21.6727</v>
@@ -1537,7 +1537,7 @@
         <v>-13.2193</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0267</v>
+        <v>1.026700000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-19.5075</v>
@@ -1546,13 +1546,13 @@
         <v>20.5343</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2520999999999997</v>
+        <v>0.7360000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.2484</v>
+        <v>-1.2605</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9964</v>
+        <v>1.9965</v>
       </c>
       <c r="V14" t="n">
         <v>-1.6592</v>
@@ -1561,7 +1561,7 @@
         <v>8.164099999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.823200000000002</v>
+        <v>-9.8232</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.1088</v>
+        <v>8.021599999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>7.4596</v>
+        <v>7.6688</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6493</v>
+        <v>0.3528</v>
       </c>
       <c r="G15" t="n">
         <v>1.9606</v>
@@ -1624,13 +1624,13 @@
         <v>2.8748</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5774</v>
+        <v>0.4902</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3798</v>
+        <v>-0.1706</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.6607</v>
       </c>
       <c r="V15" t="n">
         <v>4.9548</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.5048</v>
+        <v>6.238</v>
       </c>
       <c r="E16" t="n">
         <v>3.3497</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1551</v>
+        <v>2.8883</v>
       </c>
       <c r="G16" t="n">
         <v>4.0002</v>
@@ -1702,13 +1702,13 @@
         <v>2.2588</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5313</v>
+        <v>0.2645</v>
       </c>
       <c r="T16" t="n">
         <v>-0.651</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1823</v>
+        <v>0.9155</v>
       </c>
       <c r="V16" t="n">
         <v>1.7679</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.4256</v>
+        <v>4.5302</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7834</v>
+        <v>3.888</v>
       </c>
       <c r="F17" t="n">
         <v>0.6422</v>
@@ -1780,10 +1780,10 @@
         <v>2.0534</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5579</v>
+        <v>-0.4533</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.651</v>
+        <v>-0.5464</v>
       </c>
       <c r="U17" t="n">
         <v>0.0931</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0016</v>
+        <v>3.2684</v>
       </c>
       <c r="E18" t="n">
         <v>1.82</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1816</v>
+        <v>1.4484</v>
       </c>
       <c r="G18" t="n">
         <v>2.7816</v>
@@ -1858,13 +1858,13 @@
         <v>1.6427</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3986</v>
+        <v>0.6654</v>
       </c>
       <c r="T18" t="n">
         <v>0.244</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1547</v>
+        <v>0.4215</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5893</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7989</v>
+        <v>2.0674</v>
       </c>
       <c r="E19" t="n">
-        <v>0.07480000000000001</v>
+        <v>2.1598</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7241</v>
+        <v>-0.0924</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3359</v>
+        <v>2.2856</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7624</v>
+        <v>0.6909</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4265</v>
+        <v>1.5947</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2842</v>
+        <v>2.2482</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.3538</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3552</v>
+        <v>1.8944</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6201</v>
+        <v>0.0375</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6913</v>
+        <v>0.3371</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0713</v>
+        <v>-0.2996</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2321</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2588</v>
+        <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3134</v>
+        <v>0.371</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8173</v>
+        <v>-0.2403</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4961</v>
+        <v>0.6113</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.4107</v>
+        <v>-0.5893</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4107</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6193</v>
+        <v>1.0666</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7414</v>
+        <v>-0.6575</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.122</v>
+        <v>1.7241</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2856</v>
+        <v>-0.3359</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6909</v>
+        <v>-0.7624</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5947</v>
+        <v>0.4265</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2482</v>
+        <v>0.2842</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3538</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8944</v>
+        <v>0.3552</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0375</v>
+        <v>-0.6201</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3371</v>
+        <v>-0.6913</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2996</v>
+        <v>0.0713</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.2321</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0267</v>
+        <v>2.2588</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.077</v>
+        <v>0.5812</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6587</v>
+        <v>0.0851</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5817</v>
+        <v>0.4961</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5893</v>
+        <v>-0.4107</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7679</v>
+        <v>-0.4107</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K.  BAOKO</t>
+          <t>M. ANDREATTA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3012</v>
+        <v>0.6157</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2848</v>
+        <v>0.0643</v>
       </c>
       <c r="F21" t="n">
-        <v>0.586</v>
+        <v>0.5513</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1284</v>
+        <v>1.5833</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2334</v>
+        <v>0.415</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.105</v>
+        <v>1.1683</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8381</v>
+        <v>3.0609</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7592</v>
+        <v>2.2191</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0789</v>
+        <v>0.8418</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7097</v>
+        <v>-1.4777</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5258</v>
+        <v>-1.8041</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1839</v>
+        <v>0.3264</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.8748</v>
+        <v>1.6427</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.1068</v>
+        <v>-1.2321</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2321</v>
+        <v>2.8748</v>
       </c>
       <c r="S21" t="n">
-        <v>1.869</v>
+        <v>-0.6945</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5651</v>
+        <v>-0.3682</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3039</v>
+        <v>-0.3263</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1786</v>
+        <v>-1.9158</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4189</v>
+        <v>-1.3963</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2402</v>
+        <v>-0.5195</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. ANDREATTA</t>
+          <t>K. NEWTON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1397</v>
+        <v>-0.2963</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1449</v>
+        <v>0.6687</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2845</v>
+        <v>-0.965</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5833</v>
+        <v>0.8285</v>
       </c>
       <c r="H22" t="n">
-        <v>0.415</v>
+        <v>-1.3628</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1683</v>
+        <v>2.1913</v>
       </c>
       <c r="J22" t="n">
-        <v>3.0609</v>
+        <v>1.5827</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2191</v>
+        <v>-0.5611</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8418</v>
+        <v>2.1438</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4777</v>
+        <v>-0.7542</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.8041</v>
+        <v>-0.8017</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3264</v>
+        <v>0.0475</v>
       </c>
       <c r="P22" t="n">
-        <v>1.6427</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8748</v>
+        <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1705</v>
+        <v>-0.6054</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5774</v>
+        <v>-0.4767</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5931</v>
+        <v>-0.1287</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.9158</v>
+        <v>-0.5195</v>
       </c>
       <c r="W22" t="n">
-        <v>-1.3963</v>
+        <v>0.5893</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5195</v>
+        <v>-1.1088</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. NEWTON</t>
+          <t>V. RODRIGUEZ GIL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7584</v>
+        <v>-0.7653</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3549</v>
+        <v>-0.9755</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1132</v>
+        <v>0.2102</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8285</v>
+        <v>-0.7488</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3628</v>
+        <v>-0.9277</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1913</v>
+        <v>0.1789</v>
       </c>
       <c r="J23" t="n">
-        <v>1.5827</v>
+        <v>-0.6384</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5611</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>2.1438</v>
+        <v>0.0395</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7542</v>
+        <v>-0.1104</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8017</v>
+        <v>-0.2498</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0475</v>
+        <v>0.1395</v>
       </c>
       <c r="P23" t="n">
+        <v>0.2053</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.2053</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.2218</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.1317</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.0901</v>
+      </c>
+      <c r="V23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-1.0267</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.0267</v>
-      </c>
-      <c r="S23" t="n">
-        <v>-1.0674</v>
-      </c>
-      <c r="T23" t="n">
-        <v>-0.7905</v>
-      </c>
-      <c r="U23" t="n">
-        <v>-0.2769</v>
-      </c>
-      <c r="V23" t="n">
-        <v>-0.5195</v>
-      </c>
       <c r="W23" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V. RODRIGUEZ GIL</t>
+          <t>K.  BAOKO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-1.1319</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9755</v>
+        <v>-1.54</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1806</v>
+        <v>0.4082</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7488</v>
+        <v>0.1284</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9277</v>
+        <v>0.2334</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1789</v>
+        <v>-0.105</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6384</v>
+        <v>0.8381</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.7592</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0395</v>
+        <v>0.0789</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1104</v>
+        <v>-0.7097</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2498</v>
+        <v>-0.5258</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1395</v>
+        <v>-0.1839</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2053</v>
+        <v>-2.8748</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2053</v>
+        <v>-4.1068</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2515</v>
+        <v>0.4359</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1317</v>
+        <v>0.3098</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1197</v>
+        <v>0.126</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.4776</v>
+        <v>-1.3433</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5923</v>
+        <v>-1.4877</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1147</v>
+        <v>0.1444</v>
       </c>
       <c r="G25" t="n">
         <v>-1.2261</v>
@@ -2404,13 +2404,13 @@
         <v>0.2053</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4568</v>
+        <v>-0.3225</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1976</v>
+        <v>-0.093</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2592</v>
+        <v>-0.2295</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.5125</v>
+        <v>-6.9145</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.6207</v>
+        <v>-5.9931</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.8918</v>
+        <v>-0.9214</v>
       </c>
       <c r="G26" t="n">
         <v>-1.1527</v>
@@ -2482,13 +2482,13 @@
         <v>1.6427</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8566</v>
+        <v>-0.2586</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5851</v>
+        <v>0.0425</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2715</v>
+        <v>-0.3011</v>
       </c>
       <c r="V26" t="n">
         <v>-1.807</v>
@@ -2515,10 +2515,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>15.3565</v>
+        <v>15.3566</v>
       </c>
       <c r="E27" t="n">
-        <v>8.965600000000002</v>
+        <v>8.9655</v>
       </c>
       <c r="F27" t="n">
         <v>6.3911</v>
@@ -2536,13 +2536,13 @@
         <v>21.673</v>
       </c>
       <c r="K27" t="n">
-        <v>8.453700000000001</v>
+        <v>8.4537</v>
       </c>
       <c r="L27" t="n">
         <v>13.2193</v>
       </c>
       <c r="M27" t="n">
-        <v>-7.200900000000001</v>
+        <v>-7.200899999999999</v>
       </c>
       <c r="N27" t="n">
         <v>-7.3349</v>
@@ -2560,22 +2560,22 @@
         <v>19.5075</v>
       </c>
       <c r="S27" t="n">
-        <v>0.2519999999999996</v>
+        <v>0.2521000000000002</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.9964</v>
+        <v>-1.9965</v>
       </c>
       <c r="U27" t="n">
-        <v>2.2486</v>
+        <v>2.2485</v>
       </c>
       <c r="V27" t="n">
         <v>1.659</v>
       </c>
       <c r="W27" t="n">
-        <v>9.8231</v>
+        <v>9.823100000000002</v>
       </c>
       <c r="X27" t="n">
-        <v>-8.164100000000001</v>
+        <v>-8.164099999999999</v>
       </c>
     </row>
   </sheetData>
